--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_2/epoch_120/per_file_predictions_epoch_120.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_2/epoch_120/per_file_predictions_epoch_120.xlsx
@@ -808,769 +808,769 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9252,0.0762,0.0045,0.0011</t>
-  </si>
-  <si>
-    <t>0.9124,0.0350,0.0229,0.0064</t>
-  </si>
-  <si>
-    <t>0.8893,0.0827,0.0098,0.0028</t>
-  </si>
-  <si>
-    <t>0.9807,0.0045,0.0028,0.0014</t>
-  </si>
-  <si>
-    <t>0.9021,0.0889,0.0040,0.0019</t>
-  </si>
-  <si>
-    <t>0.9538,0.0469,0.0006,0.0004</t>
-  </si>
-  <si>
-    <t>0.9083,0.0657,0.0051,0.0037</t>
-  </si>
-  <si>
-    <t>0.8776,0.1280,0.0066,0.0033</t>
-  </si>
-  <si>
-    <t>0.9239,0.0580,0.0035,0.0033</t>
-  </si>
-  <si>
-    <t>0.9488,0.0562,0.0009,0.0005</t>
-  </si>
-  <si>
-    <t>0.9148,0.0873,0.0039,0.0018</t>
-  </si>
-  <si>
-    <t>0.7793,0.2653,0.0033,0.0013</t>
-  </si>
-  <si>
-    <t>0.9943,0.0017,0.0021,0.0001</t>
-  </si>
-  <si>
-    <t>0.9586,0.0132,0.0275,0.0004</t>
-  </si>
-  <si>
-    <t>0.9690,0.0185,0.0067,0.0003</t>
-  </si>
-  <si>
-    <t>0.9795,0.0068,0.0057,0.0004</t>
-  </si>
-  <si>
-    <t>0.9462,0.0311,0.0186,0.0005</t>
-  </si>
-  <si>
-    <t>0.9397,0.0904,0.0026,0.0002</t>
-  </si>
-  <si>
-    <t>0.8253,0.2000,0.0184,0.0014</t>
-  </si>
-  <si>
-    <t>0.8806,0.1545,0.0053,0.0006</t>
-  </si>
-  <si>
-    <t>0.0480,0.9649,0.0073,0.0006</t>
-  </si>
-  <si>
-    <t>0.8909,0.1780,0.0042,0.0002</t>
-  </si>
-  <si>
-    <t>0.9962,0.0004,0.0021,0.0000</t>
-  </si>
-  <si>
-    <t>0.9931,0.0005,0.0069,0.0001</t>
-  </si>
-  <si>
-    <t>0.9679,0.0014,0.0593,0.0002</t>
-  </si>
-  <si>
-    <t>0.9829,0.0016,0.0194,0.0002</t>
-  </si>
-  <si>
-    <t>0.9604,0.0050,0.0372,0.0007</t>
-  </si>
-  <si>
-    <t>0.8841,0.0081,0.1543,0.0028</t>
-  </si>
-  <si>
-    <t>0.4164,0.0099,0.7220,0.0004</t>
-  </si>
-  <si>
-    <t>0.9611,0.0331,0.0066,0.0003</t>
-  </si>
-  <si>
-    <t>0.8888,0.1157,0.0091,0.0008</t>
-  </si>
-  <si>
-    <t>0.0156,0.0331,0.9781,0.0012</t>
-  </si>
-  <si>
-    <t>0.9138,0.0808,0.0085,0.0005</t>
-  </si>
-  <si>
-    <t>0.9100,0.1099,0.0032,0.0009</t>
-  </si>
-  <si>
-    <t>0.5890,0.4818,0.0340,0.0029</t>
-  </si>
-  <si>
-    <t>0.9693,0.0202,0.0011,0.0010</t>
-  </si>
-  <si>
-    <t>0.9315,0.0727,0.0135,0.0007</t>
-  </si>
-  <si>
-    <t>0.6540,0.0286,0.3053,0.0008</t>
-  </si>
-  <si>
-    <t>0.9958,0.0004,0.0025,0.0001</t>
-  </si>
-  <si>
-    <t>0.9527,0.0056,0.0548,0.0010</t>
-  </si>
-  <si>
-    <t>0.9913,0.0012,0.0049,0.0004</t>
-  </si>
-  <si>
-    <t>0.8901,0.0070,0.1515,0.0003</t>
-  </si>
-  <si>
-    <t>0.6691,0.1751,0.0668,0.0033</t>
-  </si>
-  <si>
-    <t>0.9169,0.0020,0.1622,0.0006</t>
-  </si>
-  <si>
-    <t>0.9488,0.0273,0.0083,0.0013</t>
-  </si>
-  <si>
-    <t>0.9779,0.0223,0.0011,0.0001</t>
-  </si>
-  <si>
-    <t>0.9439,0.0556,0.0027,0.0000</t>
-  </si>
-  <si>
-    <t>0.9251,0.0686,0.0115,0.0005</t>
-  </si>
-  <si>
-    <t>0.0597,0.0139,0.9588,0.0004</t>
-  </si>
-  <si>
-    <t>0.0827,0.0146,0.9375,0.0013</t>
-  </si>
-  <si>
-    <t>0.9600,0.0050,0.0392,0.0004</t>
-  </si>
-  <si>
-    <t>0.5896,0.0085,0.6078,0.0008</t>
-  </si>
-  <si>
-    <t>0.2189,0.0569,0.7487,0.0012</t>
-  </si>
-  <si>
-    <t>0.8793,0.0347,0.0735,0.0004</t>
-  </si>
-  <si>
-    <t>0.9180,0.1106,0.0018,0.0006</t>
-  </si>
-  <si>
-    <t>0.8300,0.2092,0.0092,0.0018</t>
-  </si>
-  <si>
-    <t>0.9519,0.0153,0.0014,0.0036</t>
-  </si>
-  <si>
-    <t>0.3505,0.5719,0.1372,0.0024</t>
-  </si>
-  <si>
-    <t>0.9686,0.0215,0.0007,0.0010</t>
-  </si>
-  <si>
-    <t>0.9062,0.0881,0.0025,0.0019</t>
-  </si>
-  <si>
-    <t>0.9054,0.1238,0.0041,0.0008</t>
-  </si>
-  <si>
-    <t>0.5212,0.0463,0.6289,0.0039</t>
-  </si>
-  <si>
-    <t>0.0717,0.0186,0.9440,0.0006</t>
-  </si>
-  <si>
-    <t>0.8083,0.0166,0.2581,0.0036</t>
-  </si>
-  <si>
-    <t>0.9157,0.0126,0.1103,0.0006</t>
-  </si>
-  <si>
-    <t>0.8695,0.0070,0.2391,0.0014</t>
-  </si>
-  <si>
-    <t>0.9268,0.0851,0.0087,0.0003</t>
-  </si>
-  <si>
-    <t>0.5192,0.7092,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.9420,0.0416,0.0109,0.0004</t>
-  </si>
-  <si>
-    <t>0.9463,0.0339,0.0061,0.0011</t>
-  </si>
-  <si>
-    <t>0.1007,0.1283,0.8055,0.0014</t>
-  </si>
-  <si>
-    <t>0.0259,0.8815,0.4640,0.0004</t>
-  </si>
-  <si>
-    <t>0.9006,0.0038,0.1717,0.0003</t>
-  </si>
-  <si>
-    <t>0.2187,0.7143,0.0465,0.0004</t>
-  </si>
-  <si>
-    <t>0.2680,0.4498,0.1874,0.0005</t>
-  </si>
-  <si>
-    <t>0.9209,0.0120,0.0439,0.0109</t>
-  </si>
-  <si>
-    <t>0.9331,0.0143,0.0095,0.0131</t>
-  </si>
-  <si>
-    <t>0.9547,0.0118,0.0069,0.0128</t>
-  </si>
-  <si>
-    <t>0.9586,0.0179,0.0046,0.0027</t>
-  </si>
-  <si>
-    <t>0.9754,0.0040,0.0025,0.0054</t>
-  </si>
-  <si>
-    <t>0.9766,0.0014,0.0005,0.0096</t>
-  </si>
-  <si>
-    <t>0.7915,0.0775,0.0987,0.0005</t>
-  </si>
-  <si>
-    <t>0.6643,0.0346,0.2280,0.0009</t>
-  </si>
-  <si>
-    <t>0.8460,0.0241,0.1367,0.0011</t>
-  </si>
-  <si>
-    <t>0.8806,0.0058,0.2420,0.0009</t>
-  </si>
-  <si>
-    <t>0.7112,0.2711,0.0164,0.0001</t>
-  </si>
-  <si>
-    <t>0.9388,0.0257,0.0252,0.0004</t>
-  </si>
-  <si>
-    <t>0.9713,0.0306,0.0013,0.0005</t>
-  </si>
-  <si>
-    <t>0.9133,0.0920,0.0033,0.0020</t>
-  </si>
-  <si>
-    <t>0.8341,0.2026,0.0017,0.0009</t>
-  </si>
-  <si>
-    <t>0.8991,0.0866,0.0015,0.0012</t>
-  </si>
-  <si>
-    <t>0.9432,0.0191,0.0008,0.0033</t>
-  </si>
-  <si>
-    <t>0.8153,0.2245,0.0068,0.0016</t>
-  </si>
-  <si>
-    <t>0.9109,0.0502,0.0024,0.0039</t>
-  </si>
-  <si>
-    <t>0.9399,0.0555,0.0031,0.0017</t>
-  </si>
-  <si>
-    <t>0.9765,0.0180,0.0006,0.0004</t>
-  </si>
-  <si>
-    <t>0.5785,0.5048,0.0142,0.0023</t>
-  </si>
-  <si>
-    <t>0.9062,0.0708,0.0025,0.0025</t>
-  </si>
-  <si>
-    <t>0.9198,0.0625,0.0032,0.0024</t>
-  </si>
-  <si>
-    <t>0.9324,0.0509,0.0020,0.0018</t>
-  </si>
-  <si>
-    <t>0.9509,0.0508,0.0021,0.0006</t>
-  </si>
-  <si>
-    <t>0.9216,0.0739,0.0038,0.0019</t>
-  </si>
-  <si>
-    <t>0.9153,0.0504,0.0012,0.0025</t>
-  </si>
-  <si>
-    <t>0.0485,0.0238,0.9725,0.0006</t>
-  </si>
-  <si>
-    <t>0.9861,0.0019,0.0095,0.0003</t>
-  </si>
-  <si>
-    <t>0.9930,0.0012,0.0037,0.0001</t>
-  </si>
-  <si>
-    <t>0.9047,0.0020,0.1800,0.0003</t>
-  </si>
-  <si>
-    <t>0.5556,0.6544,0.0059,0.0005</t>
-  </si>
-  <si>
-    <t>0.4979,0.6901,0.0032,0.0003</t>
-  </si>
-  <si>
-    <t>0.7720,0.3330,0.0086,0.0012</t>
-  </si>
-  <si>
-    <t>0.9317,0.0818,0.0023,0.0004</t>
-  </si>
-  <si>
-    <t>0.6788,0.4859,0.0032,0.0004</t>
-  </si>
-  <si>
-    <t>0.1319,0.9058,0.0116,0.0005</t>
-  </si>
-  <si>
-    <t>0.8200,0.2042,0.0098,0.0021</t>
-  </si>
-  <si>
-    <t>0.9348,0.0480,0.0171,0.0012</t>
-  </si>
-  <si>
-    <t>0.8203,0.0447,0.1206,0.0015</t>
-  </si>
-  <si>
-    <t>0.9858,0.0024,0.0094,0.0002</t>
-  </si>
-  <si>
-    <t>0.9678,0.0155,0.0097,0.0005</t>
-  </si>
-  <si>
-    <t>0.9534,0.0221,0.0134,0.0013</t>
-  </si>
-  <si>
-    <t>0.9707,0.0324,0.0017,0.0000</t>
-  </si>
-  <si>
-    <t>0.8901,0.1173,0.0083,0.0001</t>
-  </si>
-  <si>
-    <t>0.9709,0.0164,0.0065,0.0005</t>
-  </si>
-  <si>
-    <t>0.3270,0.2697,0.1174,0.0002</t>
-  </si>
-  <si>
-    <t>0.9771,0.0291,0.0015,0.0001</t>
-  </si>
-  <si>
-    <t>0.9481,0.0458,0.0047,0.0007</t>
-  </si>
-  <si>
-    <t>0.6655,0.3289,0.0201,0.0041</t>
-  </si>
-  <si>
-    <t>0.9832,0.0114,0.0011,0.0003</t>
-  </si>
-  <si>
-    <t>0.9373,0.0612,0.0024,0.0014</t>
-  </si>
-  <si>
-    <t>0.8032,0.2663,0.0056,0.0011</t>
-  </si>
-  <si>
-    <t>0.8756,0.1044,0.0104,0.0024</t>
-  </si>
-  <si>
-    <t>0.9478,0.0525,0.0022,0.0009</t>
-  </si>
-  <si>
-    <t>0.8866,0.1241,0.0153,0.0020</t>
-  </si>
-  <si>
-    <t>0.9052,0.1214,0.0027,0.0005</t>
-  </si>
-  <si>
-    <t>0.8308,0.2239,0.0069,0.0016</t>
-  </si>
-  <si>
-    <t>0.8961,0.0144,0.1481,0.0006</t>
-  </si>
-  <si>
-    <t>0.8445,0.0077,0.2275,0.0007</t>
-  </si>
-  <si>
-    <t>0.6992,0.0229,0.3212,0.0017</t>
-  </si>
-  <si>
-    <t>0.9350,0.0088,0.0664,0.0006</t>
-  </si>
-  <si>
-    <t>0.9868,0.0031,0.0057,0.0004</t>
-  </si>
-  <si>
-    <t>0.9251,0.0254,0.0277,0.0016</t>
-  </si>
-  <si>
-    <t>0.8487,0.0258,0.1738,0.0020</t>
-  </si>
-  <si>
-    <t>0.9551,0.0334,0.0050,0.0008</t>
-  </si>
-  <si>
-    <t>0.9857,0.0040,0.0019,0.0016</t>
-  </si>
-  <si>
-    <t>0.6892,0.0155,0.0508,0.2481</t>
-  </si>
-  <si>
-    <t>0.8949,0.0184,0.0241,0.0297</t>
-  </si>
-  <si>
-    <t>0.9541,0.0135,0.0089,0.0035</t>
-  </si>
-  <si>
-    <t>0.1087,0.6461,0.0924,0.0034</t>
-  </si>
-  <si>
-    <t>0.8745,0.1757,0.0053,0.0013</t>
-  </si>
-  <si>
-    <t>0.9638,0.0268,0.0012,0.0007</t>
-  </si>
-  <si>
-    <t>0.9615,0.0324,0.0015,0.0009</t>
-  </si>
-  <si>
-    <t>0.9213,0.0547,0.0037,0.0018</t>
-  </si>
-  <si>
-    <t>0.9489,0.0377,0.0017,0.0012</t>
-  </si>
-  <si>
-    <t>0.8777,0.1082,0.0109,0.0022</t>
-  </si>
-  <si>
-    <t>0.8633,0.1848,0.0015,0.0009</t>
-  </si>
-  <si>
-    <t>0.2685,0.1495,0.7662,0.0155</t>
-  </si>
-  <si>
-    <t>0.7674,0.2096,0.0206,0.0050</t>
-  </si>
-  <si>
-    <t>0.8838,0.0753,0.0100,0.0054</t>
-  </si>
-  <si>
-    <t>0.9773,0.0166,0.0027,0.0003</t>
-  </si>
-  <si>
-    <t>0.9734,0.0124,0.0031,0.0011</t>
-  </si>
-  <si>
-    <t>0.9173,0.0786,0.0045,0.0010</t>
-  </si>
-  <si>
-    <t>0.9385,0.0562,0.0089,0.0005</t>
-  </si>
-  <si>
-    <t>0.6587,0.4660,0.0079,0.0006</t>
-  </si>
-  <si>
-    <t>0.7253,0.3240,0.0217,0.0013</t>
-  </si>
-  <si>
-    <t>0.8129,0.1985,0.0145,0.0022</t>
-  </si>
-  <si>
-    <t>0.9296,0.0989,0.0019,0.0007</t>
-  </si>
-  <si>
-    <t>0.8499,0.2183,0.0041,0.0010</t>
-  </si>
-  <si>
-    <t>0.9397,0.0575,0.0014,0.0008</t>
-  </si>
-  <si>
-    <t>0.8973,0.0710,0.0033,0.0023</t>
-  </si>
-  <si>
-    <t>0.9882,0.0051,0.0003,0.0006</t>
-  </si>
-  <si>
-    <t>0.9234,0.0629,0.0019,0.0022</t>
-  </si>
-  <si>
-    <t>0.9705,0.0198,0.0012,0.0009</t>
-  </si>
-  <si>
-    <t>0.8051,0.2729,0.0090,0.0010</t>
-  </si>
-  <si>
-    <t>0.8912,0.1543,0.0016,0.0003</t>
-  </si>
-  <si>
-    <t>0.9296,0.0861,0.0009,0.0002</t>
-  </si>
-  <si>
-    <t>0.6115,0.2805,0.1896,0.0113</t>
-  </si>
-  <si>
-    <t>0.8845,0.1335,0.0041,0.0014</t>
-  </si>
-  <si>
-    <t>0.9136,0.0587,0.0064,0.0034</t>
-  </si>
-  <si>
-    <t>0.6058,0.4807,0.0354,0.0039</t>
-  </si>
-  <si>
-    <t>0.9055,0.1164,0.0053,0.0008</t>
-  </si>
-  <si>
-    <t>0.0078,0.3605,0.9601,0.0013</t>
-  </si>
-  <si>
-    <t>0.9676,0.0196,0.0010,0.0009</t>
-  </si>
-  <si>
-    <t>0.6976,0.0112,0.4666,0.0004</t>
-  </si>
-  <si>
-    <t>0.7034,0.0215,0.3964,0.0053</t>
-  </si>
-  <si>
-    <t>0.9594,0.0086,0.0270,0.0008</t>
-  </si>
-  <si>
-    <t>0.1110,0.0590,0.8900,0.0005</t>
-  </si>
-  <si>
-    <t>0.8830,0.0090,0.1675,0.0013</t>
-  </si>
-  <si>
-    <t>0.2352,0.0024,0.8720,0.0012</t>
-  </si>
-  <si>
-    <t>0.8714,0.0322,0.1569,0.0040</t>
-  </si>
-  <si>
-    <t>0.9726,0.0101,0.0098,0.0004</t>
-  </si>
-  <si>
-    <t>0.8337,0.0441,0.1353,0.0025</t>
-  </si>
-  <si>
-    <t>0.9206,0.0415,0.0194,0.0021</t>
-  </si>
-  <si>
-    <t>0.8817,0.0828,0.0368,0.0011</t>
-  </si>
-  <si>
-    <t>0.9833,0.0059,0.0049,0.0002</t>
-  </si>
-  <si>
-    <t>0.9457,0.0202,0.0244,0.0006</t>
-  </si>
-  <si>
-    <t>0.9414,0.0289,0.0172,0.0020</t>
-  </si>
-  <si>
-    <t>0.9437,0.0196,0.0270,0.0017</t>
-  </si>
-  <si>
-    <t>0.9372,0.0747,0.0024,0.0006</t>
-  </si>
-  <si>
-    <t>0.7588,0.3926,0.0013,0.0004</t>
-  </si>
-  <si>
-    <t>0.6713,0.4387,0.0254,0.0024</t>
-  </si>
-  <si>
-    <t>0.9399,0.0622,0.0020,0.0009</t>
-  </si>
-  <si>
-    <t>0.9409,0.0725,0.0020,0.0005</t>
-  </si>
-  <si>
-    <t>0.9397,0.0300,0.0139,0.0006</t>
-  </si>
-  <si>
-    <t>0.9859,0.0063,0.0030,0.0002</t>
-  </si>
-  <si>
-    <t>0.9927,0.0012,0.0029,0.0002</t>
-  </si>
-  <si>
-    <t>0.9812,0.0040,0.0107,0.0004</t>
-  </si>
-  <si>
-    <t>0.8209,0.0261,0.1453,0.0117</t>
-  </si>
-  <si>
-    <t>0.6609,0.0312,0.3768,0.0016</t>
-  </si>
-  <si>
-    <t>0.9869,0.0010,0.0144,0.0005</t>
-  </si>
-  <si>
-    <t>0.9910,0.0006,0.0128,0.0001</t>
-  </si>
-  <si>
-    <t>0.8638,0.0435,0.0714,0.0003</t>
-  </si>
-  <si>
-    <t>0.9677,0.0025,0.0431,0.0002</t>
-  </si>
-  <si>
-    <t>0.9610,0.0245,0.0006,0.0011</t>
-  </si>
-  <si>
-    <t>0.8782,0.1509,0.0027,0.0008</t>
-  </si>
-  <si>
-    <t>0.7272,0.3445,0.0076,0.0020</t>
-  </si>
-  <si>
-    <t>0.9207,0.1122,0.0031,0.0006</t>
-  </si>
-  <si>
-    <t>0.9511,0.0440,0.0026,0.0013</t>
-  </si>
-  <si>
-    <t>0.8870,0.1297,0.0030,0.0015</t>
-  </si>
-  <si>
-    <t>0.8661,0.1250,0.0071,0.0034</t>
-  </si>
-  <si>
-    <t>0.7403,0.3376,0.0045,0.0011</t>
-  </si>
-  <si>
-    <t>0.4897,0.4834,0.0854,0.0011</t>
-  </si>
-  <si>
-    <t>0.8430,0.1516,0.0106,0.0024</t>
-  </si>
-  <si>
-    <t>0.8916,0.1132,0.0104,0.0012</t>
-  </si>
-  <si>
-    <t>0.8794,0.0106,0.1479,0.0004</t>
-  </si>
-  <si>
-    <t>0.0346,0.1265,0.9300,0.0042</t>
-  </si>
-  <si>
-    <t>0.8319,0.0281,0.1608,0.0006</t>
-  </si>
-  <si>
-    <t>0.0921,0.0031,0.9697,0.0003</t>
-  </si>
-  <si>
-    <t>0.9600,0.0025,0.0553,0.0005</t>
-  </si>
-  <si>
-    <t>0.1704,0.0236,0.8287,0.0037</t>
-  </si>
-  <si>
-    <t>0.8966,0.0024,0.1876,0.0009</t>
-  </si>
-  <si>
-    <t>0.9930,0.0015,0.0031,0.0001</t>
-  </si>
-  <si>
-    <t>0.9714,0.0056,0.0090,0.0016</t>
-  </si>
-  <si>
-    <t>0.9865,0.0033,0.0069,0.0003</t>
-  </si>
-  <si>
-    <t>0.9722,0.0078,0.0163,0.0003</t>
-  </si>
-  <si>
-    <t>0.8940,0.0893,0.0015,0.0010</t>
-  </si>
-  <si>
-    <t>0.8494,0.2255,0.0036,0.0009</t>
-  </si>
-  <si>
-    <t>0.8461,0.1577,0.0057,0.0018</t>
-  </si>
-  <si>
-    <t>0.9155,0.0718,0.0035,0.0015</t>
-  </si>
-  <si>
-    <t>0.9113,0.1043,0.0023,0.0007</t>
-  </si>
-  <si>
-    <t>0.9325,0.0597,0.0017,0.0015</t>
-  </si>
-  <si>
-    <t>0.9710,0.0322,0.0009,0.0003</t>
-  </si>
-  <si>
-    <t>0.9522,0.0566,0.0010,0.0005</t>
-  </si>
-  <si>
-    <t>0.9110,0.0218,0.0733,0.0007</t>
-  </si>
-  <si>
-    <t>0.1293,0.0169,0.9249,0.0002</t>
-  </si>
-  <si>
-    <t>0.4456,0.1616,0.3668,0.0034</t>
-  </si>
-  <si>
-    <t>0.9840,0.0039,0.0085,0.0003</t>
-  </si>
-  <si>
-    <t>0.9646,0.0046,0.0344,0.0003</t>
-  </si>
-  <si>
-    <t>0.9882,0.0020,0.0063,0.0003</t>
-  </si>
-  <si>
-    <t>0.9824,0.0028,0.0158,0.0005</t>
-  </si>
-  <si>
-    <t>0.9822,0.0009,0.0292,0.0003</t>
-  </si>
-  <si>
-    <t>0.9570,0.0273,0.0023,0.0010</t>
-  </si>
-  <si>
-    <t>0.9714,0.0070,0.0062,0.0030</t>
-  </si>
-  <si>
-    <t>0.8994,0.0493,0.0126,0.0205</t>
-  </si>
-  <si>
-    <t>0.8114,0.0120,0.0269,0.1352</t>
-  </si>
-  <si>
-    <t>0.9436,0.0095,0.0078,0.0164</t>
-  </si>
-  <si>
-    <t>0.8379,0.1557,0.0259,0.0013</t>
+    <t>0.9813,0.0027,0.0026,0.0063</t>
+  </si>
+  <si>
+    <t>0.0248,0.0001,0.0001,0.9943</t>
+  </si>
+  <si>
+    <t>0.6847,0.0070,0.0008,0.2555</t>
+  </si>
+  <si>
+    <t>0.0179,0.0109,0.0003,0.9918</t>
+  </si>
+  <si>
+    <t>0.9980,0.0006,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9933,0.0040,0.0004,0.0008</t>
+  </si>
+  <si>
+    <t>0.9965,0.0002,0.0002,0.0022</t>
+  </si>
+  <si>
+    <t>0.9969,0.0003,0.0001,0.0025</t>
+  </si>
+  <si>
+    <t>0.9938,0.0021,0.0001,0.0010</t>
+  </si>
+  <si>
+    <t>0.9946,0.0030,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.9893,0.0040,0.0010,0.0018</t>
+  </si>
+  <si>
+    <t>0.9990,0.0001,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9835,0.0018,0.0168,0.0003</t>
+  </si>
+  <si>
+    <t>0.1503,0.0079,0.9022,0.0011</t>
+  </si>
+  <si>
+    <t>0.1040,0.0004,0.9695,0.0000</t>
+  </si>
+  <si>
+    <t>0.0479,0.0080,0.9411,0.0090</t>
+  </si>
+  <si>
+    <t>0.9532,0.0095,0.0320,0.0039</t>
+  </si>
+  <si>
+    <t>0.0094,0.9846,0.0038,0.0039</t>
+  </si>
+  <si>
+    <t>0.0117,0.9799,0.0039,0.0083</t>
+  </si>
+  <si>
+    <t>0.0950,0.9265,0.0104,0.0058</t>
+  </si>
+  <si>
+    <t>0.0310,0.9594,0.0045,0.0077</t>
+  </si>
+  <si>
+    <t>0.0027,0.9918,0.0129,0.0023</t>
+  </si>
+  <si>
+    <t>0.3093,0.0103,0.7331,0.0080</t>
+  </si>
+  <si>
+    <t>0.4818,0.0031,0.4487,0.0290</t>
+  </si>
+  <si>
+    <t>0.0164,0.0021,0.9728,0.0056</t>
+  </si>
+  <si>
+    <t>0.1493,0.0096,0.8797,0.0042</t>
+  </si>
+  <si>
+    <t>0.4564,0.0031,0.6356,0.0042</t>
+  </si>
+  <si>
+    <t>0.0044,0.0043,0.9864,0.0038</t>
+  </si>
+  <si>
+    <t>0.0047,0.0011,0.9932,0.0010</t>
+  </si>
+  <si>
+    <t>0.5566,0.4911,0.0116,0.0169</t>
+  </si>
+  <si>
+    <t>0.4478,0.1785,0.5379,0.0187</t>
+  </si>
+  <si>
+    <t>0.0010,0.0123,0.9974,0.0031</t>
+  </si>
+  <si>
+    <t>0.0169,0.9334,0.0644,0.0002</t>
+  </si>
+  <si>
+    <t>0.7757,0.2501,0.0283,0.0375</t>
+  </si>
+  <si>
+    <t>0.8591,0.0961,0.0476,0.0116</t>
+  </si>
+  <si>
+    <t>0.6949,0.3149,0.0315,0.0011</t>
+  </si>
+  <si>
+    <t>0.0182,0.9793,0.0233,0.0007</t>
+  </si>
+  <si>
+    <t>0.0100,0.0247,0.9537,0.0095</t>
+  </si>
+  <si>
+    <t>0.0274,0.0197,0.9199,0.0785</t>
+  </si>
+  <si>
+    <t>0.0550,0.0685,0.9335,0.0068</t>
+  </si>
+  <si>
+    <t>0.1009,0.0021,0.9176,0.0062</t>
+  </si>
+  <si>
+    <t>0.0065,0.7456,0.9701,0.0024</t>
+  </si>
+  <si>
+    <t>0.0131,0.8534,0.0966,0.0006</t>
+  </si>
+  <si>
+    <t>0.0062,0.0030,0.9911,0.0015</t>
+  </si>
+  <si>
+    <t>0.4519,0.2347,0.0098,0.2626</t>
+  </si>
+  <si>
+    <t>0.0015,0.9903,0.0010,0.0289</t>
+  </si>
+  <si>
+    <t>0.0044,0.9855,0.0084,0.0067</t>
+  </si>
+  <si>
+    <t>0.0089,0.9858,0.0075,0.0017</t>
+  </si>
+  <si>
+    <t>0.0006,0.0049,0.9946,0.0085</t>
+  </si>
+  <si>
+    <t>0.0014,0.0579,0.9953,0.0009</t>
+  </si>
+  <si>
+    <t>0.0259,0.0015,0.9667,0.0045</t>
+  </si>
+  <si>
+    <t>0.0068,0.0034,0.9911,0.0009</t>
+  </si>
+  <si>
+    <t>0.0036,0.0043,0.9924,0.0020</t>
+  </si>
+  <si>
+    <t>0.0070,0.0170,0.9844,0.0020</t>
+  </si>
+  <si>
+    <t>0.9660,0.0321,0.0026,0.0023</t>
+  </si>
+  <si>
+    <t>0.9570,0.0179,0.0220,0.0054</t>
+  </si>
+  <si>
+    <t>0.9774,0.0162,0.0019,0.0038</t>
+  </si>
+  <si>
+    <t>0.0289,0.0109,0.9837,0.0009</t>
+  </si>
+  <si>
+    <t>0.9962,0.0009,0.0010,0.0004</t>
+  </si>
+  <si>
+    <t>0.9926,0.0018,0.0012,0.0025</t>
+  </si>
+  <si>
+    <t>0.9295,0.0876,0.0045,0.0021</t>
+  </si>
+  <si>
+    <t>0.0006,0.9720,0.9778,0.0003</t>
+  </si>
+  <si>
+    <t>0.0099,0.0052,0.9868,0.0031</t>
+  </si>
+  <si>
+    <t>0.0036,0.0073,0.9903,0.0060</t>
+  </si>
+  <si>
+    <t>0.0027,0.9531,0.9462,0.0008</t>
+  </si>
+  <si>
+    <t>0.0022,0.0073,0.9943,0.0013</t>
+  </si>
+  <si>
+    <t>0.0199,0.9810,0.0076,0.0004</t>
+  </si>
+  <si>
+    <t>0.0062,0.9929,0.0010,0.0002</t>
+  </si>
+  <si>
+    <t>0.9383,0.0201,0.0565,0.0085</t>
+  </si>
+  <si>
+    <t>0.2284,0.0509,0.7871,0.0160</t>
+  </si>
+  <si>
+    <t>0.0056,0.0524,0.9907,0.0040</t>
+  </si>
+  <si>
+    <t>0.0046,0.9402,0.7368,0.0010</t>
+  </si>
+  <si>
+    <t>0.0013,0.9555,0.9434,0.0006</t>
+  </si>
+  <si>
+    <t>0.0013,0.9900,0.4056,0.0011</t>
+  </si>
+  <si>
+    <t>0.0004,0.9818,0.9638,0.0001</t>
+  </si>
+  <si>
+    <t>0.0073,0.0005,0.0091,0.9910</t>
+  </si>
+  <si>
+    <t>0.0028,0.0013,0.0004,0.9982</t>
+  </si>
+  <si>
+    <t>0.0049,0.0014,0.0009,0.9969</t>
+  </si>
+  <si>
+    <t>0.0116,0.0016,0.0016,0.9942</t>
+  </si>
+  <si>
+    <t>0.0076,0.0002,0.0018,0.9952</t>
+  </si>
+  <si>
+    <t>0.0069,0.0011,0.0011,0.9957</t>
+  </si>
+  <si>
+    <t>0.0010,0.9815,0.9214,0.0013</t>
+  </si>
+  <si>
+    <t>0.0013,0.0646,0.9975,0.0003</t>
+  </si>
+  <si>
+    <t>0.0143,0.2312,0.9436,0.0025</t>
+  </si>
+  <si>
+    <t>0.0029,0.8027,0.9656,0.0012</t>
+  </si>
+  <si>
+    <t>0.0006,0.9720,0.9746,0.0002</t>
+  </si>
+  <si>
+    <t>0.0093,0.9492,0.0552,0.0025</t>
+  </si>
+  <si>
+    <t>0.9955,0.0006,0.0008,0.0019</t>
+  </si>
+  <si>
+    <t>0.9910,0.0075,0.0009,0.0004</t>
+  </si>
+  <si>
+    <t>0.9794,0.0196,0.0014,0.0015</t>
+  </si>
+  <si>
+    <t>0.9940,0.0021,0.0002,0.0013</t>
+  </si>
+  <si>
+    <t>0.9939,0.0010,0.0003,0.0022</t>
+  </si>
+  <si>
+    <t>0.9874,0.0088,0.0007,0.0010</t>
+  </si>
+  <si>
+    <t>0.9636,0.0248,0.0132,0.0035</t>
+  </si>
+  <si>
+    <t>0.9953,0.0024,0.0007,0.0006</t>
+  </si>
+  <si>
+    <t>0.9991,0.0001,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9909,0.0025,0.0022,0.0033</t>
+  </si>
+  <si>
+    <t>0.9986,0.0002,0.0001,0.0008</t>
+  </si>
+  <si>
+    <t>0.9987,0.0000,0.0000,0.0014</t>
+  </si>
+  <si>
+    <t>0.9942,0.0010,0.0005,0.0025</t>
+  </si>
+  <si>
+    <t>0.9749,0.0169,0.0021,0.0030</t>
+  </si>
+  <si>
+    <t>0.9928,0.0027,0.0006,0.0018</t>
+  </si>
+  <si>
+    <t>0.9975,0.0004,0.0002,0.0012</t>
+  </si>
+  <si>
+    <t>0.0166,0.0130,0.9866,0.0009</t>
+  </si>
+  <si>
+    <t>0.0048,0.0163,0.9814,0.0079</t>
+  </si>
+  <si>
+    <t>0.9415,0.0005,0.0173,0.0130</t>
+  </si>
+  <si>
+    <t>0.0171,0.0011,0.9807,0.0024</t>
+  </si>
+  <si>
+    <t>0.0086,0.9901,0.0018,0.0010</t>
+  </si>
+  <si>
+    <t>0.0019,0.9964,0.0008,0.0005</t>
+  </si>
+  <si>
+    <t>0.0116,0.9805,0.0061,0.0058</t>
+  </si>
+  <si>
+    <t>0.0982,0.9433,0.0047,0.0008</t>
+  </si>
+  <si>
+    <t>0.0023,0.9947,0.0007,0.0012</t>
+  </si>
+  <si>
+    <t>0.0054,0.9920,0.0016,0.0012</t>
+  </si>
+  <si>
+    <t>0.6714,0.5016,0.0053,0.0028</t>
+  </si>
+  <si>
+    <t>0.9224,0.0087,0.0377,0.0181</t>
+  </si>
+  <si>
+    <t>0.0819,0.0009,0.9514,0.0013</t>
+  </si>
+  <si>
+    <t>0.8251,0.0074,0.1712,0.0141</t>
+  </si>
+  <si>
+    <t>0.6091,0.0179,0.5127,0.0091</t>
+  </si>
+  <si>
+    <t>0.0783,0.0859,0.1585,0.8307</t>
+  </si>
+  <si>
+    <t>0.0018,0.9958,0.0018,0.0007</t>
+  </si>
+  <si>
+    <t>0.0089,0.9803,0.0092,0.0036</t>
+  </si>
+  <si>
+    <t>0.0013,0.9948,0.0035,0.0008</t>
+  </si>
+  <si>
+    <t>0.0018,0.7809,0.9450,0.0014</t>
+  </si>
+  <si>
+    <t>0.0189,0.9745,0.0144,0.0004</t>
+  </si>
+  <si>
+    <t>0.8369,0.1859,0.0123,0.0026</t>
+  </si>
+  <si>
+    <t>0.2759,0.6907,0.1270,0.0181</t>
+  </si>
+  <si>
+    <t>0.9941,0.0011,0.0014,0.0021</t>
+  </si>
+  <si>
+    <t>0.9957,0.0003,0.0006,0.0020</t>
+  </si>
+  <si>
+    <t>0.9952,0.0005,0.0010,0.0013</t>
+  </si>
+  <si>
+    <t>0.9831,0.0054,0.0032,0.0029</t>
+  </si>
+  <si>
+    <t>0.9949,0.0006,0.0007,0.0030</t>
+  </si>
+  <si>
+    <t>0.9757,0.0017,0.0271,0.0014</t>
+  </si>
+  <si>
+    <t>0.9900,0.0016,0.0005,0.0027</t>
+  </si>
+  <si>
+    <t>0.9940,0.0003,0.0017,0.0027</t>
+  </si>
+  <si>
+    <t>0.0024,0.2102,0.9839,0.0059</t>
+  </si>
+  <si>
+    <t>0.0032,0.2366,0.9883,0.0011</t>
+  </si>
+  <si>
+    <t>0.0017,0.0984,0.9907,0.0017</t>
+  </si>
+  <si>
+    <t>0.0256,0.0174,0.9676,0.0024</t>
+  </si>
+  <si>
+    <t>0.9927,0.0009,0.0022,0.0006</t>
+  </si>
+  <si>
+    <t>0.6067,0.0653,0.1590,0.0972</t>
+  </si>
+  <si>
+    <t>0.3078,0.0059,0.7232,0.0144</t>
+  </si>
+  <si>
+    <t>0.9533,0.0037,0.0427,0.0033</t>
+  </si>
+  <si>
+    <t>0.0276,0.0001,0.0003,0.9935</t>
+  </si>
+  <si>
+    <t>0.0007,0.0004,0.0033,0.9983</t>
+  </si>
+  <si>
+    <t>0.0037,0.0187,0.0014,0.9954</t>
+  </si>
+  <si>
+    <t>0.0058,0.0002,0.0007,0.9972</t>
+  </si>
+  <si>
+    <t>0.0007,0.9894,0.7243,0.0009</t>
+  </si>
+  <si>
+    <t>0.9946,0.0007,0.0010,0.0016</t>
+  </si>
+  <si>
+    <t>0.1295,0.8789,0.0054,0.0219</t>
+  </si>
+  <si>
+    <t>0.9900,0.0019,0.0021,0.0039</t>
+  </si>
+  <si>
+    <t>0.6893,0.4591,0.0034,0.0010</t>
+  </si>
+  <si>
+    <t>0.9885,0.0007,0.0015,0.0054</t>
+  </si>
+  <si>
+    <t>0.2993,0.0061,0.0085,0.8260</t>
+  </si>
+  <si>
+    <t>0.9949,0.0002,0.0006,0.0029</t>
+  </si>
+  <si>
+    <t>0.0043,0.0218,0.9641,0.1158</t>
+  </si>
+  <si>
+    <t>0.9425,0.0004,0.0001,0.1329</t>
+  </si>
+  <si>
+    <t>0.9855,0.0004,0.0004,0.0151</t>
+  </si>
+  <si>
+    <t>0.7238,0.3610,0.0069,0.0034</t>
+  </si>
+  <si>
+    <t>0.9864,0.0016,0.0025,0.0045</t>
+  </si>
+  <si>
+    <t>0.9693,0.0229,0.0023,0.0037</t>
+  </si>
+  <si>
+    <t>0.7165,0.2353,0.0259,0.0107</t>
+  </si>
+  <si>
+    <t>0.9792,0.0075,0.0096,0.0006</t>
+  </si>
+  <si>
+    <t>0.9945,0.0012,0.0025,0.0002</t>
+  </si>
+  <si>
+    <t>0.9960,0.0008,0.0003,0.0014</t>
+  </si>
+  <si>
+    <t>0.9940,0.0015,0.0012,0.0017</t>
+  </si>
+  <si>
+    <t>0.9862,0.0037,0.0027,0.0048</t>
+  </si>
+  <si>
+    <t>0.9976,0.0001,0.0003,0.0015</t>
+  </si>
+  <si>
+    <t>0.9734,0.0011,0.0248,0.0031</t>
+  </si>
+  <si>
+    <t>0.9922,0.0004,0.0002,0.0062</t>
+  </si>
+  <si>
+    <t>0.9952,0.0004,0.0013,0.0018</t>
+  </si>
+  <si>
+    <t>0.9921,0.0005,0.0007,0.0046</t>
+  </si>
+  <si>
+    <t>0.6137,0.4320,0.0074,0.0128</t>
+  </si>
+  <si>
+    <t>0.8437,0.2462,0.0012,0.0009</t>
+  </si>
+  <si>
+    <t>0.8538,0.2230,0.0047,0.0015</t>
+  </si>
+  <si>
+    <t>0.0165,0.1656,0.9722,0.0070</t>
+  </si>
+  <si>
+    <t>0.9656,0.0423,0.0003,0.0011</t>
+  </si>
+  <si>
+    <t>0.9425,0.0303,0.0091,0.0080</t>
+  </si>
+  <si>
+    <t>0.9940,0.0010,0.0010,0.0022</t>
+  </si>
+  <si>
+    <t>0.6854,0.4382,0.0016,0.0037</t>
+  </si>
+  <si>
+    <t>0.0009,0.0120,0.9983,0.0011</t>
+  </si>
+  <si>
+    <t>0.9515,0.0330,0.0148,0.0027</t>
+  </si>
+  <si>
+    <t>0.0305,0.0020,0.9776,0.0005</t>
+  </si>
+  <si>
+    <t>0.0023,0.0473,0.9939,0.0033</t>
+  </si>
+  <si>
+    <t>0.0006,0.0020,0.9980,0.0012</t>
+  </si>
+  <si>
+    <t>0.0031,0.2380,0.9950,0.0007</t>
+  </si>
+  <si>
+    <t>0.0063,0.0085,0.9889,0.0016</t>
+  </si>
+  <si>
+    <t>0.0025,0.0016,0.9918,0.0057</t>
+  </si>
+  <si>
+    <t>0.0022,0.0073,0.9912,0.0060</t>
+  </si>
+  <si>
+    <t>0.0312,0.0044,0.9601,0.0026</t>
+  </si>
+  <si>
+    <t>0.4476,0.0251,0.6076,0.0137</t>
+  </si>
+  <si>
+    <t>0.4761,0.0087,0.6547,0.0050</t>
+  </si>
+  <si>
+    <t>0.3857,0.5641,0.0776,0.0065</t>
+  </si>
+  <si>
+    <t>0.2654,0.0996,0.5674,0.0105</t>
+  </si>
+  <si>
+    <t>0.4450,0.0409,0.5336,0.0022</t>
+  </si>
+  <si>
+    <t>0.1115,0.1364,0.6428,0.0650</t>
+  </si>
+  <si>
+    <t>0.1360,0.0255,0.8346,0.0220</t>
+  </si>
+  <si>
+    <t>0.0373,0.9732,0.0013,0.0016</t>
+  </si>
+  <si>
+    <t>0.0078,0.9897,0.0012,0.0022</t>
+  </si>
+  <si>
+    <t>0.0520,0.9655,0.0005,0.0024</t>
+  </si>
+  <si>
+    <t>0.9914,0.0048,0.0005,0.0020</t>
+  </si>
+  <si>
+    <t>0.8578,0.2501,0.0029,0.0019</t>
+  </si>
+  <si>
+    <t>0.9583,0.0121,0.0093,0.0041</t>
+  </si>
+  <si>
+    <t>0.9713,0.0019,0.0271,0.0019</t>
+  </si>
+  <si>
+    <t>0.9389,0.0036,0.0101,0.0294</t>
+  </si>
+  <si>
+    <t>0.7064,0.0143,0.2518,0.0487</t>
+  </si>
+  <si>
+    <t>0.7387,0.0009,0.0420,0.1157</t>
+  </si>
+  <si>
+    <t>0.0041,0.0046,0.9922,0.0028</t>
+  </si>
+  <si>
+    <t>0.0087,0.0232,0.9453,0.0230</t>
+  </si>
+  <si>
+    <t>0.0208,0.0172,0.9798,0.0011</t>
+  </si>
+  <si>
+    <t>0.2139,0.0058,0.8528,0.0020</t>
+  </si>
+  <si>
+    <t>0.0357,0.5600,0.5059,0.0062</t>
+  </si>
+  <si>
+    <t>0.9956,0.0009,0.0004,0.0015</t>
+  </si>
+  <si>
+    <t>0.9909,0.0036,0.0015,0.0024</t>
+  </si>
+  <si>
+    <t>0.9889,0.0049,0.0019,0.0023</t>
+  </si>
+  <si>
+    <t>0.9970,0.0008,0.0006,0.0006</t>
+  </si>
+  <si>
+    <t>0.9800,0.0080,0.0022,0.0038</t>
+  </si>
+  <si>
+    <t>0.9957,0.0006,0.0004,0.0018</t>
+  </si>
+  <si>
+    <t>0.9980,0.0003,0.0001,0.0008</t>
+  </si>
+  <si>
+    <t>0.9935,0.0007,0.0004,0.0036</t>
+  </si>
+  <si>
+    <t>0.0023,0.1582,0.9943,0.0029</t>
+  </si>
+  <si>
+    <t>0.0743,0.4035,0.7802,0.0135</t>
+  </si>
+  <si>
+    <t>0.9721,0.0094,0.0120,0.0037</t>
+  </si>
+  <si>
+    <t>0.0022,0.0006,0.9977,0.0002</t>
+  </si>
+  <si>
+    <t>0.0005,0.0016,0.9974,0.0029</t>
+  </si>
+  <si>
+    <t>0.0010,0.0112,0.9958,0.0026</t>
+  </si>
+  <si>
+    <t>0.0086,0.0053,0.9939,0.0004</t>
+  </si>
+  <si>
+    <t>0.0020,0.0014,0.9910,0.0049</t>
+  </si>
+  <si>
+    <t>0.0014,0.0014,0.9947,0.0026</t>
+  </si>
+  <si>
+    <t>0.0057,0.0174,0.9807,0.0058</t>
+  </si>
+  <si>
+    <t>0.0143,0.0080,0.9714,0.0058</t>
+  </si>
+  <si>
+    <t>0.8017,0.0029,0.3549,0.0021</t>
+  </si>
+  <si>
+    <t>0.6347,0.0009,0.3408,0.0126</t>
+  </si>
+  <si>
+    <t>0.9242,0.0038,0.0933,0.0033</t>
+  </si>
+  <si>
+    <t>0.9692,0.0270,0.0008,0.0017</t>
+  </si>
+  <si>
+    <t>0.9954,0.0015,0.0003,0.0006</t>
+  </si>
+  <si>
+    <t>0.9955,0.0005,0.0001,0.0027</t>
+  </si>
+  <si>
+    <t>0.9897,0.0061,0.0011,0.0010</t>
+  </si>
+  <si>
+    <t>0.9875,0.0007,0.0003,0.0124</t>
+  </si>
+  <si>
+    <t>0.9972,0.0007,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9929,0.0036,0.0002,0.0008</t>
+  </si>
+  <si>
+    <t>0.9939,0.0008,0.0002,0.0032</t>
+  </si>
+  <si>
+    <t>0.0354,0.0773,0.9228,0.0039</t>
+  </si>
+  <si>
+    <t>0.0041,0.0277,0.9911,0.0021</t>
+  </si>
+  <si>
+    <t>0.0288,0.2480,0.8849,0.0105</t>
+  </si>
+  <si>
+    <t>0.0345,0.0100,0.9580,0.0025</t>
+  </si>
+  <si>
+    <t>0.0036,0.0004,0.9934,0.0013</t>
+  </si>
+  <si>
+    <t>0.0441,0.0305,0.9122,0.0479</t>
+  </si>
+  <si>
+    <t>0.3494,0.0050,0.7137,0.0067</t>
+  </si>
+  <si>
+    <t>0.0839,0.0032,0.9303,0.0045</t>
+  </si>
+  <si>
+    <t>0.7198,0.0006,0.0031,0.4161</t>
+  </si>
+  <si>
+    <t>0.0227,0.0145,0.0010,0.9882</t>
+  </si>
+  <si>
+    <t>0.3576,0.0013,0.0013,0.8401</t>
+  </si>
+  <si>
+    <t>0.0007,0.0001,0.0002,0.9995</t>
+  </si>
+  <si>
+    <t>0.0018,0.0004,0.0008,0.9986</t>
+  </si>
+  <si>
+    <t>0.9818,0.0027,0.0015,0.0081</t>
   </si>
 </sst>
 </file>
@@ -1967,7 +1967,7 @@
         <v>260</v>
       </c>
       <c r="C3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D3" t="s">
         <v>265</v>
@@ -1995,7 +1995,7 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D5" t="s">
         <v>267</v>
@@ -2135,7 +2135,7 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D15" t="s">
         <v>277</v>
@@ -2149,7 +2149,7 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
         <v>278</v>
@@ -2163,7 +2163,7 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D17" t="s">
         <v>279</v>
@@ -2191,7 +2191,7 @@
         <v>262</v>
       </c>
       <c r="C19" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D19" t="s">
         <v>281</v>
@@ -2205,7 +2205,7 @@
         <v>262</v>
       </c>
       <c r="C20" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D20" t="s">
         <v>282</v>
@@ -2219,7 +2219,7 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D21" t="s">
         <v>283</v>
@@ -2247,7 +2247,7 @@
         <v>262</v>
       </c>
       <c r="C23" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D23" t="s">
         <v>285</v>
@@ -2261,7 +2261,7 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D24" t="s">
         <v>286</v>
@@ -2289,7 +2289,7 @@
         <v>261</v>
       </c>
       <c r="C26" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D26" t="s">
         <v>288</v>
@@ -2303,7 +2303,7 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D27" t="s">
         <v>289</v>
@@ -2317,7 +2317,7 @@
         <v>261</v>
       </c>
       <c r="C28" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D28" t="s">
         <v>290</v>
@@ -2331,7 +2331,7 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D29" t="s">
         <v>291</v>
@@ -2373,7 +2373,7 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D32" t="s">
         <v>294</v>
@@ -2401,7 +2401,7 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D34" t="s">
         <v>296</v>
@@ -2457,7 +2457,7 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D38" t="s">
         <v>300</v>
@@ -2471,7 +2471,7 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D39" t="s">
         <v>301</v>
@@ -2485,7 +2485,7 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D40" t="s">
         <v>302</v>
@@ -2499,7 +2499,7 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D41" t="s">
         <v>303</v>
@@ -2513,7 +2513,7 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D42" t="s">
         <v>304</v>
@@ -2527,7 +2527,7 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D43" t="s">
         <v>305</v>
@@ -2541,7 +2541,7 @@
         <v>262</v>
       </c>
       <c r="C44" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D44" t="s">
         <v>306</v>
@@ -2555,7 +2555,7 @@
         <v>261</v>
       </c>
       <c r="C45" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D45" t="s">
         <v>307</v>
@@ -2583,7 +2583,7 @@
         <v>262</v>
       </c>
       <c r="C47" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D47" t="s">
         <v>309</v>
@@ -2597,7 +2597,7 @@
         <v>262</v>
       </c>
       <c r="C48" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D48" t="s">
         <v>310</v>
@@ -2611,7 +2611,7 @@
         <v>262</v>
       </c>
       <c r="C49" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D49" t="s">
         <v>311</v>
@@ -2653,7 +2653,7 @@
         <v>261</v>
       </c>
       <c r="C52" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D52" t="s">
         <v>314</v>
@@ -2695,7 +2695,7 @@
         <v>261</v>
       </c>
       <c r="C55" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D55" t="s">
         <v>317</v>
@@ -2751,7 +2751,7 @@
         <v>261</v>
       </c>
       <c r="C59" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D59" t="s">
         <v>321</v>
@@ -2807,7 +2807,7 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D63" t="s">
         <v>325</v>
@@ -2835,7 +2835,7 @@
         <v>261</v>
       </c>
       <c r="C65" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D65" t="s">
         <v>327</v>
@@ -2849,7 +2849,7 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D66" t="s">
         <v>328</v>
@@ -2863,7 +2863,7 @@
         <v>261</v>
       </c>
       <c r="C67" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D67" t="s">
         <v>329</v>
@@ -2877,7 +2877,7 @@
         <v>262</v>
       </c>
       <c r="C68" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D68" t="s">
         <v>330</v>
@@ -2919,7 +2919,7 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D71" t="s">
         <v>333</v>
@@ -2947,7 +2947,7 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D73" t="s">
         <v>335</v>
@@ -2961,7 +2961,7 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
         <v>336</v>
@@ -2989,7 +2989,7 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D76" t="s">
         <v>338</v>
@@ -3003,7 +3003,7 @@
         <v>260</v>
       </c>
       <c r="C77" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D77" t="s">
         <v>339</v>
@@ -3017,7 +3017,7 @@
         <v>260</v>
       </c>
       <c r="C78" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D78" t="s">
         <v>340</v>
@@ -3031,7 +3031,7 @@
         <v>260</v>
       </c>
       <c r="C79" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D79" t="s">
         <v>341</v>
@@ -3045,7 +3045,7 @@
         <v>260</v>
       </c>
       <c r="C80" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D80" t="s">
         <v>342</v>
@@ -3059,7 +3059,7 @@
         <v>260</v>
       </c>
       <c r="C81" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D81" t="s">
         <v>343</v>
@@ -3073,7 +3073,7 @@
         <v>260</v>
       </c>
       <c r="C82" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D82" t="s">
         <v>344</v>
@@ -3087,7 +3087,7 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D83" t="s">
         <v>345</v>
@@ -3101,7 +3101,7 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D84" t="s">
         <v>346</v>
@@ -3115,7 +3115,7 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D85" t="s">
         <v>347</v>
@@ -3129,7 +3129,7 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D86" t="s">
         <v>348</v>
@@ -3143,7 +3143,7 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D87" t="s">
         <v>349</v>
@@ -3157,7 +3157,7 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D88" t="s">
         <v>350</v>
@@ -3297,7 +3297,7 @@
         <v>259</v>
       </c>
       <c r="C98" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D98" t="s">
         <v>360</v>
@@ -3409,7 +3409,7 @@
         <v>261</v>
       </c>
       <c r="C106" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D106" t="s">
         <v>368</v>
@@ -3437,7 +3437,7 @@
         <v>261</v>
       </c>
       <c r="C108" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D108" t="s">
         <v>370</v>
@@ -3479,7 +3479,7 @@
         <v>262</v>
       </c>
       <c r="C111" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D111" t="s">
         <v>373</v>
@@ -3493,7 +3493,7 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D112" t="s">
         <v>374</v>
@@ -3507,7 +3507,7 @@
         <v>262</v>
       </c>
       <c r="C113" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D113" t="s">
         <v>375</v>
@@ -3535,7 +3535,7 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D115" t="s">
         <v>377</v>
@@ -3563,7 +3563,7 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
         <v>379</v>
@@ -3591,7 +3591,7 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D119" t="s">
         <v>381</v>
@@ -3605,7 +3605,7 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D120" t="s">
         <v>382</v>
@@ -3619,7 +3619,7 @@
         <v>262</v>
       </c>
       <c r="C121" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D121" t="s">
         <v>383</v>
@@ -3633,7 +3633,7 @@
         <v>262</v>
       </c>
       <c r="C122" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D122" t="s">
         <v>384</v>
@@ -3647,7 +3647,7 @@
         <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D123" t="s">
         <v>385</v>
@@ -3661,7 +3661,7 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D124" t="s">
         <v>386</v>
@@ -3675,7 +3675,7 @@
         <v>262</v>
       </c>
       <c r="C125" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D125" t="s">
         <v>387</v>
@@ -3703,7 +3703,7 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D127" t="s">
         <v>389</v>
@@ -3829,7 +3829,7 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D136" t="s">
         <v>398</v>
@@ -3843,7 +3843,7 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D137" t="s">
         <v>399</v>
@@ -3857,7 +3857,7 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D138" t="s">
         <v>400</v>
@@ -3871,7 +3871,7 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D139" t="s">
         <v>401</v>
@@ -3913,7 +3913,7 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
         <v>404</v>
@@ -3941,7 +3941,7 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D144" t="s">
         <v>406</v>
@@ -3955,7 +3955,7 @@
         <v>260</v>
       </c>
       <c r="C145" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D145" t="s">
         <v>407</v>
@@ -3969,7 +3969,7 @@
         <v>260</v>
       </c>
       <c r="C146" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D146" t="s">
         <v>408</v>
@@ -3983,7 +3983,7 @@
         <v>260</v>
       </c>
       <c r="C147" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D147" t="s">
         <v>409</v>
@@ -3997,7 +3997,7 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D148" t="s">
         <v>410</v>
@@ -4025,7 +4025,7 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D150" t="s">
         <v>412</v>
@@ -4081,7 +4081,7 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D154" t="s">
         <v>416</v>
@@ -4389,7 +4389,7 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D176" t="s">
         <v>438</v>
@@ -4487,7 +4487,7 @@
         <v>261</v>
       </c>
       <c r="C183" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D183" t="s">
         <v>445</v>
@@ -4501,7 +4501,7 @@
         <v>261</v>
       </c>
       <c r="C184" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D184" t="s">
         <v>446</v>
@@ -4515,7 +4515,7 @@
         <v>261</v>
       </c>
       <c r="C185" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D185" t="s">
         <v>447</v>
@@ -4543,7 +4543,7 @@
         <v>261</v>
       </c>
       <c r="C187" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D187" t="s">
         <v>449</v>
@@ -4571,7 +4571,7 @@
         <v>261</v>
       </c>
       <c r="C189" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D189" t="s">
         <v>451</v>
@@ -4585,7 +4585,7 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
         <v>452</v>
@@ -4599,7 +4599,7 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D191" t="s">
         <v>453</v>
@@ -4613,7 +4613,7 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
         <v>454</v>
@@ -4627,7 +4627,7 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D193" t="s">
         <v>455</v>
@@ -4641,7 +4641,7 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
         <v>456</v>
@@ -4655,7 +4655,7 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D195" t="s">
         <v>457</v>
@@ -4669,7 +4669,7 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D196" t="s">
         <v>458</v>
@@ -4683,7 +4683,7 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
         <v>459</v>
@@ -4697,7 +4697,7 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D198" t="s">
         <v>460</v>
@@ -4711,7 +4711,7 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D199" t="s">
         <v>461</v>
@@ -4725,7 +4725,7 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D200" t="s">
         <v>462</v>
@@ -4837,7 +4837,7 @@
         <v>261</v>
       </c>
       <c r="C208" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D208" t="s">
         <v>470</v>
@@ -4851,7 +4851,7 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D209" t="s">
         <v>471</v>
@@ -4865,7 +4865,7 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D210" t="s">
         <v>472</v>
@@ -4879,7 +4879,7 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D211" t="s">
         <v>473</v>
@@ -4893,7 +4893,7 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D212" t="s">
         <v>474</v>
@@ -5019,7 +5019,7 @@
         <v>261</v>
       </c>
       <c r="C221" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D221" t="s">
         <v>483</v>
@@ -5033,7 +5033,7 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
         <v>484</v>
@@ -5061,7 +5061,7 @@
         <v>261</v>
       </c>
       <c r="C224" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D224" t="s">
         <v>486</v>
@@ -5089,7 +5089,7 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D226" t="s">
         <v>488</v>
@@ -5117,7 +5117,7 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D228" t="s">
         <v>490</v>
@@ -5145,7 +5145,7 @@
         <v>261</v>
       </c>
       <c r="C230" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D230" t="s">
         <v>492</v>
@@ -5159,7 +5159,7 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D231" t="s">
         <v>493</v>
@@ -5327,7 +5327,7 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D243" t="s">
         <v>505</v>
@@ -5355,7 +5355,7 @@
         <v>261</v>
       </c>
       <c r="C245" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D245" t="s">
         <v>507</v>
@@ -5369,7 +5369,7 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D246" t="s">
         <v>508</v>
@@ -5383,7 +5383,7 @@
         <v>261</v>
       </c>
       <c r="C247" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D247" t="s">
         <v>509</v>
@@ -5397,7 +5397,7 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
         <v>510</v>
@@ -5411,7 +5411,7 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D249" t="s">
         <v>511</v>
@@ -5425,7 +5425,7 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D250" t="s">
         <v>512</v>
@@ -5453,7 +5453,7 @@
         <v>260</v>
       </c>
       <c r="C252" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D252" t="s">
         <v>514</v>
@@ -5467,7 +5467,7 @@
         <v>260</v>
       </c>
       <c r="C253" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D253" t="s">
         <v>515</v>
@@ -5481,7 +5481,7 @@
         <v>260</v>
       </c>
       <c r="C254" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D254" t="s">
         <v>516</v>
@@ -5495,7 +5495,7 @@
         <v>260</v>
       </c>
       <c r="C255" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D255" t="s">
         <v>517</v>
